--- a/templates/matkalasku-2026.xlsx
+++ b/templates/matkalasku-2026.xlsx
@@ -93,7 +93,7 @@
             <sz val="12"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="34"/>
+            <family val="2"/>
           </rPr>
           <t>Käyttöautoedun km-korvaus vuonna 2023: 0,13€ /km</t>
         </r>
@@ -112,7 +112,7 @@
             <sz val="12"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="34"/>
+            <family val="2"/>
           </rPr>
           <t>(vuonna 2022: 0,14€ /km)</t>
         </r>
@@ -1390,7 +1390,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="34"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
